--- a/step2-validation-check.xlsx
+++ b/step2-validation-check.xlsx
@@ -449,13 +449,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
